--- a/customer_service_forms/025_land_shipping_assessment_form--customer_service_forms.xlsx
+++ b/customer_service_forms/025_land_shipping_assessment_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'next_day'}</t>
+          <t>next_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Next Day'}</t>
+          <t>Next Day</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'two_days'}</t>
+          <t>two_days</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Two Days'}</t>
+          <t>Two Days</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'three_days'}</t>
+          <t>three_days</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Three Days'}</t>
+          <t>Three Days</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'air'}</t>
+          <t>air</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Air'}</t>
+          <t>Air</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'ground'}</t>
+          <t>ground</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Ground'}</t>
+          <t>Ground</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'rail'}</t>
+          <t>rail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Rail'}</t>
+          <t>Rail</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'credit'}</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Credit'}</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'24/7'}</t>
+          <t>24/7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '24/7'}</t>
+          <t>24/7</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'8/5'}</t>
+          <t>8/5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '8/5'}</t>
+          <t>8/5</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'9/10'}</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '9/10'}</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'partially_paid'}</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Partially Paid'}</t>
+          <t>Partially Paid</t>
         </is>
       </c>
     </row>
